--- a/5/search/FY3_Missile2_results/top10_solutions.xlsx
+++ b/5/search/FY3_Missile2_results/top10_solutions.xlsx
@@ -487,37 +487,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B2" t="n">
-        <v>117.6</v>
+        <v>126</v>
       </c>
       <c r="C2" t="n">
         <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>5558.479365870453</v>
+        <v>6000</v>
       </c>
       <c r="F2" t="n">
-        <v>-212.3484275042833</v>
+        <v>24</v>
       </c>
       <c r="G2" t="n">
         <v>700</v>
       </c>
       <c r="H2" t="n">
-        <v>5484.892593515528</v>
+        <v>6000</v>
       </c>
       <c r="I2" t="n">
-        <v>252.2601679116694</v>
+        <v>276</v>
       </c>
       <c r="J2" t="n">
-        <v>621.6</v>
+        <v>680.4</v>
       </c>
       <c r="K2" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -525,19 +525,19 @@
         <v>90</v>
       </c>
       <c r="B3" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C3" t="n">
         <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>6000</v>
       </c>
       <c r="F3" t="n">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="G3" t="n">
         <v>700</v>
@@ -546,293 +546,293 @@
         <v>6000</v>
       </c>
       <c r="I3" t="n">
-        <v>276</v>
+        <v>250</v>
       </c>
       <c r="J3" t="n">
-        <v>680.4</v>
+        <v>695.1</v>
       </c>
       <c r="K3" t="n">
-        <v>2.400000000000002</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="B4" t="n">
-        <v>114.8</v>
+        <v>118</v>
       </c>
       <c r="C4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>6000</v>
+        <v>5556.977595006067</v>
       </c>
       <c r="F4" t="n">
-        <v>214.4000000000001</v>
+        <v>-202.8666194345697</v>
       </c>
       <c r="G4" t="n">
         <v>700</v>
       </c>
       <c r="H4" t="n">
-        <v>6000</v>
+        <v>5483.140527507077</v>
       </c>
       <c r="I4" t="n">
-        <v>214.4000000000001</v>
+        <v>263.3222773263354</v>
       </c>
       <c r="J4" t="n">
-        <v>700</v>
+        <v>621.6</v>
       </c>
       <c r="K4" t="n">
-        <v>2.200000000000003</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="B5" t="n">
-        <v>95.2</v>
+        <v>138</v>
       </c>
       <c r="C5" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>6000</v>
+        <v>5568.240876488963</v>
       </c>
       <c r="F5" t="n">
-        <v>46.40000000000009</v>
+        <v>-273.9801799574198</v>
       </c>
       <c r="G5" t="n">
         <v>700</v>
       </c>
       <c r="H5" t="n">
-        <v>6000</v>
+        <v>5481.889051786756</v>
       </c>
       <c r="I5" t="n">
-        <v>236.8000000000001</v>
+        <v>271.2237840510963</v>
       </c>
       <c r="J5" t="n">
-        <v>680.4</v>
+        <v>621.6</v>
       </c>
       <c r="K5" t="n">
-        <v>2.100000000000001</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>99</v>
+        <v>121.5</v>
       </c>
       <c r="B6" t="n">
-        <v>120.4</v>
+        <v>108</v>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4419.964340298971</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-421.6161429932249</v>
+      </c>
+      <c r="G6" t="n">
+        <v>700</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4024.955425373714</v>
+      </c>
+      <c r="I6" t="n">
+        <v>222.9798212584689</v>
+      </c>
+      <c r="J6" t="n">
+        <v>459.9</v>
+      </c>
+      <c r="K6" t="n">
         <v>3</v>
-      </c>
-      <c r="E6" t="n">
-        <v>5547.966969819749</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-145.9757710162899</v>
-      </c>
-      <c r="G6" t="n">
-        <v>700</v>
-      </c>
-      <c r="H6" t="n">
-        <v>5491.462841047217</v>
-      </c>
-      <c r="I6" t="n">
-        <v>210.7772576066739</v>
-      </c>
-      <c r="J6" t="n">
-        <v>655.9</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1.899999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126</v>
+        <v>85.5</v>
       </c>
       <c r="B7" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C7" t="n">
         <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>4222.537397067561</v>
+        <v>6248.558415265813</v>
       </c>
       <c r="F7" t="n">
-        <v>-553.5326090101589</v>
+        <v>158.2341132665492</v>
       </c>
       <c r="G7" t="n">
         <v>700</v>
       </c>
       <c r="H7" t="n">
-        <v>3704.110804545599</v>
+        <v>6258.915015901888</v>
       </c>
       <c r="I7" t="n">
-        <v>160.0203800285447</v>
+        <v>289.8272013193221</v>
       </c>
       <c r="J7" t="n">
-        <v>459.9</v>
+        <v>695.1</v>
       </c>
       <c r="K7" t="n">
-        <v>1.600000000000001</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="B8" t="n">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="C8" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5544.462837802848</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-123.8515521869585</v>
+      </c>
+      <c r="G8" t="n">
+        <v>700</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5495.655284710297</v>
+      </c>
+      <c r="I8" t="n">
+        <v>184.3072100787244</v>
+      </c>
+      <c r="J8" t="n">
+        <v>655.9</v>
+      </c>
+      <c r="K8" t="n">
         <v>2</v>
-      </c>
-      <c r="E8" t="n">
-        <v>6000</v>
-      </c>
-      <c r="F8" t="n">
-        <v>24</v>
-      </c>
-      <c r="G8" t="n">
-        <v>700</v>
-      </c>
-      <c r="H8" t="n">
-        <v>6000</v>
-      </c>
-      <c r="I8" t="n">
-        <v>192</v>
-      </c>
-      <c r="J8" t="n">
-        <v>680.4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1.200000000000003</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>144</v>
+        <v>90</v>
       </c>
       <c r="B9" t="n">
-        <v>128.8</v>
+        <v>108</v>
       </c>
       <c r="C9" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>2665.555555984217</v>
+        <v>6000</v>
       </c>
       <c r="F9" t="n">
-        <v>-577.3843041513419</v>
+        <v>24</v>
       </c>
       <c r="G9" t="n">
         <v>700</v>
       </c>
       <c r="H9" t="n">
-        <v>1623.541667229285</v>
+        <v>6000</v>
       </c>
       <c r="I9" t="n">
-        <v>179.6831008013637</v>
+        <v>240</v>
       </c>
       <c r="J9" t="n">
-        <v>209.9999999999999</v>
+        <v>680.4</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B10" t="n">
-        <v>81.2</v>
+        <v>100</v>
       </c>
       <c r="C10" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>5542.710771794397</v>
+        <v>6000</v>
       </c>
       <c r="F10" t="n">
-        <v>-112.7894427722931</v>
+        <v>200</v>
       </c>
       <c r="G10" t="n">
         <v>700</v>
       </c>
       <c r="H10" t="n">
-        <v>5491.90085754933</v>
+        <v>6000</v>
       </c>
       <c r="I10" t="n">
-        <v>208.0117302530077</v>
+        <v>200</v>
       </c>
       <c r="J10" t="n">
-        <v>621.6</v>
+        <v>700</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8999999999999986</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>144</v>
+        <v>94.5</v>
       </c>
       <c r="B11" t="n">
-        <v>106.4</v>
+        <v>124</v>
       </c>
       <c r="C11" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>2556.823671940224</v>
+        <v>5766.505731113934</v>
       </c>
       <c r="F11" t="n">
-        <v>-498.3859662432337</v>
+        <v>-33.17401481021079</v>
       </c>
       <c r="G11" t="n">
         <v>700</v>
       </c>
       <c r="H11" t="n">
-        <v>1696.02958992528</v>
+        <v>5747.047875373428</v>
       </c>
       <c r="I11" t="n">
-        <v>127.0175421959578</v>
+        <v>214.061483955605</v>
       </c>
       <c r="J11" t="n">
-        <v>209.9999999999999</v>
+        <v>680.4</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7000000000000028</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
